--- a/templates/物资采购欲购清单模板_purchase_list_template.xlsx
+++ b/templates/物资采购欲购清单模板_purchase_list_template.xlsx
@@ -61,17 +61,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
-    <col min="1" max="1" width="10" customWidth="1"/>
-    <col min="2" max="2" width="19" customWidth="1"/>
+    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="2" max="2" width="27" customWidth="1"/>
     <col min="3" max="3" width="10" customWidth="1"/>
-    <col min="4" max="4" width="13" customWidth="1"/>
-    <col min="5" max="5" width="13" customWidth="1"/>
-    <col min="6" max="6" width="19" customWidth="1"/>
+    <col min="4" max="4" width="18" customWidth="1"/>
+    <col min="5" max="5" width="18" customWidth="1"/>
+    <col min="6" max="6" width="27" customWidth="1"/>
     <col min="7" max="7" width="10" customWidth="1"/>
-    <col min="8" max="8" width="11" customWidth="1"/>
-    <col min="9" max="9" width="11" customWidth="1"/>
-    <col min="10" max="10" width="11" customWidth="1"/>
-    <col min="11" max="11" width="23" customWidth="1"/>
+    <col min="8" max="8" width="15" customWidth="1"/>
+    <col min="9" max="9" width="15" customWidth="1"/>
+    <col min="10" max="10" width="15" customWidth="1"/>
+    <col min="11" max="11" width="33" customWidth="1"/>
+    <col min="12" max="12" width="15" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -130,6 +131,11 @@
           <t xml:space="preserve">备注</t>
         </is>
       </c>
+      <c r="L1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">卫生等级</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -181,6 +187,11 @@
           <t xml:space="preserve">示例行，请替换或删除</t>
         </is>
       </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A</t>
+        </is>
+      </c>
     </row>
   </sheetData>
 </worksheet>
